--- a/literature/review/NCKH_FRNFR_VongCuoi.xlsx
+++ b/literature/review/NCKH_FRNFR_VongCuoi.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -493,46 +493,58 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Câu hỏi quan trọng nhất</t>
+          <t>Bản đọc trước (Claude)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Mỗi bài: (1) chia train/test thế nào; (2) câu trùng có thể nằm ở cả train và test không; (3) oversampling / augmentation làm TRƯỚC hay SAU khi chia; (4) có kiểm định thống kê khi so model không; (5) báo loại F1 nào.</t>
+          <t>Các cột XÁC NHẬN và Q1–Q5 đã được Claude điền sẵn sau khi đọc các đoạn liên quan trong PDF (cột Ghi chú ghi độ chắc chắn). Người đọc chỉ cần mở PDF, kiểm tra nhanh các ô quan trọng (cách chia, câu trùng, oversampling, kiểm định) — ưu tiên dòng có độ chắc chắn 'thấp' / 'trung bình' — rồi ghi ĐỒNG Ý hoặc SỬA ở cột cuối. Số liệu gap chỉ tính các dòng đã có người ĐỒNG Ý / SỬA.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Bài lạc đề</t>
+          <t>Câu hỏi quan trọng nhất</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Nếu đọc thấy bài không phải phân loại yêu cầu FR/NFR: ghi 'Giữ?' = N và lý do ở Ghi chú. Không cần điền tiếp.</t>
+          <t>Mỗi bài: (1) chia train/test thế nào; (2) câu trùng có thể nằm ở cả train và test không; (3) oversampling / augmentation làm TRƯỚC hay SAU khi chia; (4) có kiểm định thống kê khi so model không; (5) báo loại F1 nào.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>QA Q1–Q5</t>
+          <t>Bài lạc đề</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>0/1/2 mỗi tiêu chí: Q1 mục tiêu rõ · Q2 dataset mô tả và truy cập được · Q3 đánh giá chặt chẽ (cách chia rõ, không rò rỉ hiển nhiên) · Q4 kết quả đủ (metric phù hợp, có độ biến thiên) · Q5 nêu hạn chế + tái lập được. Tổng ≥ 6 = tổng hợp chính.</t>
+          <t>Nếu đọc thấy bài không phải phân loại yêu cầu FR/NFR: ghi 'Giữ?' = N và lý do ở Ghi chú. Không cần điền tiếp.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>QA Q1–Q5</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>0/1/2 mỗi tiêu chí: Q1 mục tiêu rõ · Q2 dataset mô tả và truy cập được · Q3 đánh giá chặt chẽ (cách chia rõ, không rò rỉ hiển nhiên) · Q4 kết quả đủ (metric phù hợp, có độ biến thiên) · Q5 nêu hạn chế + tái lập được. Tổng ≥ 6 = tổng hợp chính.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
           <t>Gap</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Tab GD3_Gap đã có 7 gap ứng viên với số liệu SƠ BỘ. Sau khi đọc xong, điền cột 'Xác nhận sau khi đọc' bằng số thật (k/N) rồi họp chọn.</t>
         </is>
@@ -549,7 +561,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ31"/>
+  <dimension ref="A1:AK31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -588,6 +600,7 @@
     <col width="16" customWidth="1" min="34" max="34"/>
     <col width="16" customWidth="1" min="35" max="35"/>
     <col width="16" customWidth="1" min="36" max="36"/>
+    <col width="16" customWidth="1" min="37" max="37"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -771,6 +784,11 @@
           <t>Ghi chú</t>
         </is>
       </c>
+      <c r="AK1" s="4" t="inlineStr">
+        <is>
+          <t>Người kiểm tra: ĐỒNG Ý / SỬA (ghi ô đã sửa)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -850,28 +868,72 @@
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>Corpus code (không phải yêu cầu)</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Y (GitHub)</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>câu trùng làm thổi phồng metric tới 100%</t>
+        </is>
+      </c>
       <c r="AH2">
         <f>IF(COUNT(AC2:AG2)=5,SUM(AC2:AG2),"")</f>
         <v/>
       </c>
       <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>Bài nền tảng cho G1 · Claude đọc (độ chắc chắn: cao)</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -943,28 +1005,87 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr"/>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>Dataset riêng IoT healthcare (104 yêu cầu, 8 lớp)</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>multi-class (gồm Functional)</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Hybrid KNN + luật</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>không rõ</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>không rõ</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>không dùng</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>chỉ accuracy</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>accuracy 75,9–85%</t>
+        </is>
+      </c>
+      <c r="AC3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1</v>
+      </c>
       <c r="AH3">
         <f>IF(COUNT(AC3:AG3)=5,SUM(AC3:AG3),"")</f>
         <v/>
       </c>
       <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>Dataset rất nhỏ; nhóm ensemble nhưng thực chất là lai KNN + luật · Claude đọc (độ chắc chắn: trung bình)</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1036,28 +1157,87 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>Dataset riêng 600 câu FR (domain bảo hiểm)</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>multi-class (11 lớp FR)</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Weighted voting ensemble (accuracy làm trọng số)</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>70/30 phân tầng, một lần</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>không rõ</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>không dùng</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>chủ yếu accuracy</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>accuracy 79,8% (TF-IDF)</t>
+        </is>
+      </c>
+      <c r="AC4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
       <c r="AH4">
         <f>IF(COUNT(AC4:AG4)=5,SUM(AC4:AG4),"")</f>
         <v/>
       </c>
       <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>Phân loại FR con, không phải FR/NFR · Claude đọc (độ chắc chắn: trung bình)</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1137,28 +1317,87 @@
           <t>Xử lý mất cân bằng</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr"/>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>Dataset riêng + PROMISE</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>binary FR/NFR + multi-label con</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ensemble BERT/DistilBERT/RoBERTa + attention fusion</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>35/35/30 ngẫu nhiên; 5-fold</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Y (chia ngẫu nhiên, không khử trùng)</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Y (dấu hiệu: oversampling để cân bằng dataset rồi mới chia)</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>F1 + accuracy</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>Y (paired t-test 10 lần chạy)</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>accuracy 95%, F1 0,94</t>
+        </is>
+      </c>
+      <c r="AC5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1</v>
+      </c>
       <c r="AH5">
         <f>IF(COUNT(AC5:AG5)=5,SUM(AC5:AG5),"")</f>
         <v/>
       </c>
       <c r="AI5" t="inlineStr"/>
-      <c r="AJ5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>Cần đọc kỹ đoạn oversampling để chắc thứ tự · Claude đọc (độ chắc chắn: trung bình)</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1230,28 +1469,87 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr"/>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>PURE</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>binary FR/NFR</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>CNN, LSTM, BiLSTM (DL)</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>80/20 một lần</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Y (chia ngẫu nhiên, không khử trùng)</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>không dùng</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>P/R/F1 (không rõ loại)</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>BiLSTM tốt nhất về P/R/F1</t>
+        </is>
+      </c>
+      <c r="AC6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
       <c r="AH6">
         <f>IF(COUNT(AC6:AG6)=5,SUM(AC6:AG6),"")</f>
         <v/>
       </c>
       <c r="AI6" t="inlineStr"/>
-      <c r="AJ6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>Xếp nhóm ensemble do từ khóa; thực chất là so sánh DL · Claude đọc (độ chắc chắn: trung bình)</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1331,28 +1629,87 @@
           <t>Xử lý mất cân bằng</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr"/>
-      <c r="AE7" t="inlineStr"/>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>PROMISE + 266 câu FR</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>binary + multi-class (17 lớp)</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ensemble DL (LSTM, BiLSTM, GRU, CNN) theo trọng số accuracy</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>35/35/30 cố định</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Y (chia ngẫu nhiên, không khử trùng)</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>N (random oversampling trên tập train)</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>F1 + accuracy</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>accuracy 95,7% (binary), 93,4% (multi)</t>
+        </is>
+      </c>
+      <c r="AC7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
       <c r="AH7">
         <f>IF(COUNT(AC7:AG7)=5,SUM(AC7:AG7),"")</f>
         <v/>
       </c>
       <c r="AI7" t="inlineStr"/>
-      <c r="AJ7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>Claude đọc (độ chắc chắn: trung bình)</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1432,28 +1789,87 @@
           <t>Xử lý mất cân bằng</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr"/>
-      <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
-      <c r="AD8" t="inlineStr"/>
-      <c r="AE8" t="inlineStr"/>
-      <c r="AF8" t="inlineStr"/>
-      <c r="AG8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>PROMISE (625) + PURE</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>binary FR/NFR + 6 lớp NFR</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>BERT + SVM/RF weighted voting</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>80/10/10 phân tầng, nhiều lần chia ngẫu nhiên</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Y (chia ngẫu nhiên, không khử trùng)</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>không dùng</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>F1 + accuracy</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>Y (paired t-test)</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>F1 94,1% (binary)</t>
+        </is>
+      </c>
+      <c r="AC8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1</v>
+      </c>
       <c r="AH8">
         <f>IF(COUNT(AC8:AG8)=5,SUM(AC8:AG8),"")</f>
         <v/>
       </c>
       <c r="AI8" t="inlineStr"/>
-      <c r="AJ8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>Ghi PURE 969 yêu cầu, có vẻ nhầm với PROMISE_exp · Claude đọc (độ chắc chắn: trung bình)</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1533,28 +1949,87 @@
           <t>Xử lý mất cân bằng</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
-      <c r="AD9" t="inlineStr"/>
-      <c r="AE9" t="inlineStr"/>
-      <c r="AF9" t="inlineStr"/>
-      <c r="AG9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>PROMISE_exp (969, 12 lớp)</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>multi-class (12 lớp)</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>SVM, LR, KNN, NB + Voting; hybrid SVM–BiLSTM</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>10-fold phân tầng</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Y (chia ngẫu nhiên, không khử trùng)</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Y (Hình 2 là phân bố lớp của dataset sau oversampling, rồi mới 10-fold)</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>P/R/F1 + accuracy</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>accuracy 98,79%</t>
+        </is>
+      </c>
+      <c r="AC9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
       <c r="AH9">
         <f>IF(COUNT(AC9:AG9)=5,SUM(AC9:AG9),"")</f>
         <v/>
       </c>
       <c r="AI9" t="inlineStr"/>
-      <c r="AJ9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>Ví dụ rõ nhất cho G2 · Claude đọc (độ chắc chắn: cao)</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1622,28 +2097,87 @@
       </c>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr"/>
-      <c r="AD10" t="inlineStr"/>
-      <c r="AE10" t="inlineStr"/>
-      <c r="AF10" t="inlineStr"/>
-      <c r="AG10" t="inlineStr"/>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>không rõ (có thể PROMISE)</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>binary FR/NFR</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Random Forest vs Gradient Boosting</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>không rõ (lặp 5 lần mỗi n-gram)</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>không rõ</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>không dùng</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>chủ yếu accuracy</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>accuracy &gt; 70%</t>
+        </is>
+      </c>
+      <c r="AC10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
       <c r="AH10">
         <f>IF(COUNT(AC10:AG10)=5,SUM(AC10:AG10),"")</f>
         <v/>
       </c>
       <c r="AI10" t="inlineStr"/>
-      <c r="AJ10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>Claude đọc (độ chắc chắn: thấp)</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1719,28 +2253,87 @@
           <t>Xử lý mất cân bằng</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="inlineStr"/>
-      <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="inlineStr"/>
-      <c r="AD11" t="inlineStr"/>
-      <c r="AE11" t="inlineStr"/>
-      <c r="AF11" t="inlineStr"/>
-      <c r="AG11" t="inlineStr"/>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>PROMISE + CCHIT</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>binary FR/NFR</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>FNRC (ensemble + mở rộng từ khóa)</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>70/10/20 một lần</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Y (chia ngẫu nhiên, không khử trùng)</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>không dùng</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>F-measure</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>N (chỉ link dataset PROMISE)</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>F-measure 64%</t>
+        </is>
+      </c>
+      <c r="AC11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
       <c r="AH11">
         <f>IF(COUNT(AC11:AG11)=5,SUM(AC11:AG11),"")</f>
         <v/>
       </c>
       <c r="AI11" t="inlineStr"/>
-      <c r="AJ11" t="inlineStr"/>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>Claude đọc (độ chắc chắn: trung bình)</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1812,28 +2405,87 @@
       </c>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
-      <c r="AA12" t="inlineStr"/>
-      <c r="AB12" t="inlineStr"/>
-      <c r="AC12" t="inlineStr"/>
-      <c r="AD12" t="inlineStr"/>
-      <c r="AE12" t="inlineStr"/>
-      <c r="AF12" t="inlineStr"/>
-      <c r="AG12" t="inlineStr"/>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>PROMISE NFR (625, 15 project) + Stack Overflow</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>multi-class (12 lớp gồm F)</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>MNB, SVM, LR, DT, FCN (Keras)</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>repeated k-fold CV</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Y (chia ngẫu nhiên, không khử trùng)</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>không dùng</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>P/R/F1 theo lớp + trung bình (không rõ loại)</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>Y (kiểm định khác biệt giữa 5 classifier)</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>MNB, SVM tốt nhất trên PROMISE</t>
+        </is>
+      </c>
+      <c r="AC12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1</v>
+      </c>
       <c r="AH12">
         <f>IF(COUNT(AC12:AG12)=5,SUM(AC12:AG12),"")</f>
         <v/>
       </c>
       <c r="AI12" t="inlineStr"/>
-      <c r="AJ12" t="inlineStr"/>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>Claude đọc (độ chắc chắn: trung bình)</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1909,7 +2561,11 @@
           <t>Xử lý mất cân bằng</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr"/>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
@@ -1920,17 +2576,17 @@
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr"/>
       <c r="AB13" t="inlineStr"/>
-      <c r="AC13" t="inlineStr"/>
-      <c r="AD13" t="inlineStr"/>
-      <c r="AE13" t="inlineStr"/>
-      <c r="AF13" t="inlineStr"/>
-      <c r="AG13" t="inlineStr"/>
       <c r="AH13">
         <f>IF(COUNT(AC13:AG13)=5,SUM(AC13:AG13),"")</f>
         <v/>
       </c>
       <c r="AI13" t="inlineStr"/>
-      <c r="AJ13" t="inlineStr"/>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>Lạc đề: phân loại review ứng dụng (tiếng Ả Rập), không phải đặc tả yêu cầu · Có augmentation dữ liệu · Claude đọc (độ chắc chắn: cao)</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2006,28 +2662,87 @@
           <t>Xử lý mất cân bằng</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
-      <c r="AA14" t="inlineStr"/>
-      <c r="AB14" t="inlineStr"/>
-      <c r="AC14" t="inlineStr"/>
-      <c r="AD14" t="inlineStr"/>
-      <c r="AE14" t="inlineStr"/>
-      <c r="AF14" t="inlineStr"/>
-      <c r="AG14" t="inlineStr"/>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>PROMISE_exp (969)</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>multi-class (NFR)</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>15 classifier × 4 vectorizer (BoW, TF-IDF, Hashing, Chi2)</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>5-fold CV</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Y (chia ngẫu nhiên, không khử trùng)</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>không dùng</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>F1 (không rõ loại)</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>LinearSVC + TF-IDF, F1 81,5%</t>
+        </is>
+      </c>
+      <c r="AC14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1</v>
+      </c>
       <c r="AH14">
         <f>IF(COUNT(AC14:AG14)=5,SUM(AC14:AG14),"")</f>
         <v/>
       </c>
       <c r="AI14" t="inlineStr"/>
-      <c r="AJ14" t="inlineStr"/>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>Claude đọc (độ chắc chắn: trung bình)</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2095,28 +2810,87 @@
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr"/>
-      <c r="Z15" t="inlineStr"/>
-      <c r="AA15" t="inlineStr"/>
-      <c r="AB15" t="inlineStr"/>
-      <c r="AC15" t="inlineStr"/>
-      <c r="AD15" t="inlineStr"/>
-      <c r="AE15" t="inlineStr"/>
-      <c r="AF15" t="inlineStr"/>
-      <c r="AG15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>PROMISE (NFR, 5 lớp)</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>multi-class (NFR)</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>BERT/RoBERTa + LoRA (prompt tuning)</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>80/20 + 10-fold CV (mô tả mâu thuẫn)</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Y (chia ngẫu nhiên, không khử trùng)</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>không dùng</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>F1 (không rõ loại)</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>RoBERTa-large F1 83,4%</t>
+        </is>
+      </c>
+      <c r="AC15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1</v>
+      </c>
       <c r="AH15">
         <f>IF(COUNT(AC15:AG15)=5,SUM(AC15:AG15),"")</f>
         <v/>
       </c>
       <c r="AI15" t="inlineStr"/>
-      <c r="AJ15" t="inlineStr"/>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>Có mục Threats to Validity · Claude đọc (độ chắc chắn: trung bình)</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2188,28 +2962,87 @@
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr"/>
-      <c r="AA16" t="inlineStr"/>
-      <c r="AB16" t="inlineStr"/>
-      <c r="AC16" t="inlineStr"/>
-      <c r="AD16" t="inlineStr"/>
-      <c r="AE16" t="inlineStr"/>
-      <c r="AF16" t="inlineStr"/>
-      <c r="AG16" t="inlineStr"/>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>PROMISE NFR</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>nhận diện NFR</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Word2Vec + mở rộng từ khóa (gần không giám sát)</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>không chia (dựa trên độ tương đồng)</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>không áp dụng</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>không dùng (augmentation từ khóa, không phải oversampling)</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>P/R/F</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>không nêu rõ trong đoạn đọc</t>
+        </is>
+      </c>
+      <c r="AC16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
       <c r="AH16">
         <f>IF(COUNT(AC16:AG16)=5,SUM(AC16:AG16),"")</f>
         <v/>
       </c>
       <c r="AI16" t="inlineStr"/>
-      <c r="AJ16" t="inlineStr"/>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>Claude đọc (độ chắc chắn: thấp)</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2289,28 +3122,87 @@
         </is>
       </c>
       <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr"/>
-      <c r="X17" t="inlineStr"/>
-      <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="inlineStr"/>
-      <c r="AA17" t="inlineStr"/>
-      <c r="AB17" t="inlineStr"/>
-      <c r="AC17" t="inlineStr"/>
-      <c r="AD17" t="inlineStr"/>
-      <c r="AE17" t="inlineStr"/>
-      <c r="AF17" t="inlineStr"/>
-      <c r="AG17" t="inlineStr"/>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>PROMISE (625)</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>binary FR/NFR + NFR</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>NB, kNN, LDA… + tiền xử lý chuẩn hóa</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>10-fold CV; 5 × 5-fold</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Y (chia ngẫu nhiên, không khử trùng)</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>không dùng</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>weighted P/R</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>N (p-value chỉ cho accuracy, không so model)</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>tăng 4,48% nhờ tiền xử lý</t>
+        </is>
+      </c>
+      <c r="AC17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1</v>
+      </c>
       <c r="AH17">
         <f>IF(COUNT(AC17:AG17)=5,SUM(AC17:AG17),"")</f>
         <v/>
       </c>
       <c r="AI17" t="inlineStr"/>
-      <c r="AJ17" t="inlineStr"/>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>Bài duy nhất tách riêng ảnh hưởng tiền xử lý (G7) · Claude đọc (độ chắc chắn: cao)</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2378,28 +3270,87 @@
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
-      <c r="X18" t="inlineStr"/>
-      <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr"/>
-      <c r="AA18" t="inlineStr"/>
-      <c r="AB18" t="inlineStr"/>
-      <c r="AC18" t="inlineStr"/>
-      <c r="AD18" t="inlineStr"/>
-      <c r="AE18" t="inlineStr"/>
-      <c r="AF18" t="inlineStr"/>
-      <c r="AG18" t="inlineStr"/>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>PROMISE + PURE</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>binary FR/NFR</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>LR, SVM, DT, RF, MLP</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>không rõ</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>không rõ</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>không dùng</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>chủ yếu accuracy</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>không nêu rõ trong đoạn đọc</t>
+        </is>
+      </c>
+      <c r="AC18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
       <c r="AH18">
         <f>IF(COUNT(AC18:AG18)=5,SUM(AC18:AG18),"")</f>
         <v/>
       </c>
       <c r="AI18" t="inlineStr"/>
-      <c r="AJ18" t="inlineStr"/>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>Claude đọc (độ chắc chắn: thấp)</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2471,28 +3422,87 @@
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
-      <c r="W19" t="inlineStr"/>
-      <c r="X19" t="inlineStr"/>
-      <c r="Y19" t="inlineStr"/>
-      <c r="Z19" t="inlineStr"/>
-      <c r="AA19" t="inlineStr"/>
-      <c r="AB19" t="inlineStr"/>
-      <c r="AC19" t="inlineStr"/>
-      <c r="AD19" t="inlineStr"/>
-      <c r="AE19" t="inlineStr"/>
-      <c r="AF19" t="inlineStr"/>
-      <c r="AG19" t="inlineStr"/>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>PURE</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>binary FR/NFR</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>So sánh trích xuất đặc trưng (BoW, TF-IDF) + ML</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>không rõ</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>không rõ</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>không dùng</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>chủ yếu accuracy</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>chênh 3,84% giữa hai kỹ thuật</t>
+        </is>
+      </c>
+      <c r="AC19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
       <c r="AH19">
         <f>IF(COUNT(AC19:AG19)=5,SUM(AC19:AG19),"")</f>
         <v/>
       </c>
       <c r="AI19" t="inlineStr"/>
-      <c r="AJ19" t="inlineStr"/>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>Claude đọc (độ chắc chắn: thấp)</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2568,28 +3578,87 @@
         </is>
       </c>
       <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr"/>
-      <c r="W20" t="inlineStr"/>
-      <c r="X20" t="inlineStr"/>
-      <c r="Y20" t="inlineStr"/>
-      <c r="Z20" t="inlineStr"/>
-      <c r="AA20" t="inlineStr"/>
-      <c r="AB20" t="inlineStr"/>
-      <c r="AC20" t="inlineStr"/>
-      <c r="AD20" t="inlineStr"/>
-      <c r="AE20" t="inlineStr"/>
-      <c r="AF20" t="inlineStr"/>
-      <c r="AG20" t="inlineStr"/>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>PROMISE NFR</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>binary FR/NFR + multi-class</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Zero-shot learning (mô hình ngôn ngữ)</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>không huấn luyện (zero-shot); baseline 10-fold</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>không áp dụng</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>không dùng</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>weighted F1 + theo lớp</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>Y (ANOVA + Friedman)</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>Một phần (model BERT4RE trên Zenodo)</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>F1 0,66–0,80</t>
+        </is>
+      </c>
+      <c r="AC20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1</v>
+      </c>
       <c r="AH20">
         <f>IF(COUNT(AC20:AG20)=5,SUM(AC20:AG20),"")</f>
         <v/>
       </c>
       <c r="AI20" t="inlineStr"/>
-      <c r="AJ20" t="inlineStr"/>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>Claude đọc (độ chắc chắn: cao)</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2669,28 +3738,87 @@
           <t>Xử lý mất cân bằng</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
-      <c r="W21" t="inlineStr"/>
-      <c r="X21" t="inlineStr"/>
-      <c r="Y21" t="inlineStr"/>
-      <c r="Z21" t="inlineStr"/>
-      <c r="AA21" t="inlineStr"/>
-      <c r="AB21" t="inlineStr"/>
-      <c r="AC21" t="inlineStr"/>
-      <c r="AD21" t="inlineStr"/>
-      <c r="AE21" t="inlineStr"/>
-      <c r="AF21" t="inlineStr"/>
-      <c r="AG21" t="inlineStr"/>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>PROMISE + SecReq (ePurse)</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>binary FR/NFR</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>SVM, CNN, FastText+SVM, FastText+CNN</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>70/30 holdout</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Y (chia ngẫu nhiên, không khử trùng)</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Y (dấu hiệu: nhân bản từng lớp trên dataset rồi mới chia)</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>F1 + accuracy</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>CNN accuracy 99% trên PROMISE</t>
+        </is>
+      </c>
+      <c r="AC21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
       <c r="AH21">
         <f>IF(COUNT(AC21:AG21)=5,SUM(AC21:AG21),"")</f>
         <v/>
       </c>
       <c r="AI21" t="inlineStr"/>
-      <c r="AJ21" t="inlineStr"/>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>Accuracy 99% khớp với giả thuyết rò rỉ do nhân bản · Claude đọc (độ chắc chắn: trung bình)</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2774,28 +3902,87 @@
           <t>Xử lý mất cân bằng</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr"/>
-      <c r="W22" t="inlineStr"/>
-      <c r="X22" t="inlineStr"/>
-      <c r="Y22" t="inlineStr"/>
-      <c r="Z22" t="inlineStr"/>
-      <c r="AA22" t="inlineStr"/>
-      <c r="AB22" t="inlineStr"/>
-      <c r="AC22" t="inlineStr"/>
-      <c r="AD22" t="inlineStr"/>
-      <c r="AE22" t="inlineStr"/>
-      <c r="AF22" t="inlineStr"/>
-      <c r="AG22" t="inlineStr"/>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>PROMISE + FR_NFR</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>binary FR/NFR + multi-class</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>BERT fine-tuning (khảo sát hyperparameter)</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>10-fold phân tầng</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Y (chia ngẫu nhiên, không khử trùng)</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>không dùng</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>F1 trung bình (không rõ loại)</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>Y (GitHub)</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>F1 0,99 (PROMISE), 0,97 (FR_NFR)</t>
+        </is>
+      </c>
+      <c r="AC22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>2</v>
+      </c>
       <c r="AH22">
         <f>IF(COUNT(AC22:AG22)=5,SUM(AC22:AG22),"")</f>
         <v/>
       </c>
       <c r="AI22" t="inlineStr"/>
-      <c r="AJ22" t="inlineStr"/>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>F1 0,99 rất cao · Claude đọc (độ chắc chắn: cao)</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2855,28 +4042,72 @@
           <t>Xử lý mất cân bằng</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr"/>
-      <c r="W23" t="inlineStr"/>
-      <c r="X23" t="inlineStr"/>
-      <c r="Y23" t="inlineStr"/>
-      <c r="Z23" t="inlineStr"/>
-      <c r="AA23" t="inlineStr"/>
-      <c r="AB23" t="inlineStr"/>
-      <c r="AC23" t="inlineStr"/>
-      <c r="AD23" t="inlineStr"/>
-      <c r="AE23" t="inlineStr"/>
-      <c r="AF23" t="inlineStr"/>
-      <c r="AG23" t="inlineStr"/>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>109 yêu cầu tiếng Tây Ban Nha</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>Y (Zenodo)</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>Fleiss kappa 0,78</t>
+        </is>
+      </c>
       <c r="AH23">
         <f>IF(COUNT(AC23:AG23)=5,SUM(AC23:AG23),"")</f>
         <v/>
       </c>
       <c r="AI23" t="inlineStr"/>
-      <c r="AJ23" t="inlineStr"/>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>Không có thí nghiệm phân loại (bài xây dataset tiếng Tây Ban Nha) · Dùng được làm bài nền về tái lập / FAIR · Claude đọc (độ chắc chắn: cao)</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2960,28 +4191,87 @@
           <t>Xử lý mất cân bằng</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr"/>
-      <c r="W24" t="inlineStr"/>
-      <c r="X24" t="inlineStr"/>
-      <c r="Y24" t="inlineStr"/>
-      <c r="Z24" t="inlineStr"/>
-      <c r="AA24" t="inlineStr"/>
-      <c r="AB24" t="inlineStr"/>
-      <c r="AC24" t="inlineStr"/>
-      <c r="AD24" t="inlineStr"/>
-      <c r="AE24" t="inlineStr"/>
-      <c r="AF24" t="inlineStr"/>
-      <c r="AG24" t="inlineStr"/>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>Dataset mới 9.529 FR từ 315 project (Zenodo)</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>multi-class (5 loại FR theo EARS)</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>SVM, KNN, DL</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>cross-project</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>N (chia theo project)</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>không rõ</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>P/R/F1</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>Y (Zenodo)</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>SVM P/R/F1 0,90</t>
+        </is>
+      </c>
+      <c r="AC24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>2</v>
+      </c>
       <c r="AH24">
         <f>IF(COUNT(AC24:AG24)=5,SUM(AC24:AG24),"")</f>
         <v/>
       </c>
       <c r="AI24" t="inlineStr"/>
-      <c r="AJ24" t="inlineStr"/>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>Phân loại FR con, không phải FR/NFR; mạnh về tổng quát hóa · Claude đọc (độ chắc chắn: trung bình)</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3069,28 +4359,87 @@
           <t>Xử lý mất cân bằng</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr"/>
-      <c r="W25" t="inlineStr"/>
-      <c r="X25" t="inlineStr"/>
-      <c r="Y25" t="inlineStr"/>
-      <c r="Z25" t="inlineStr"/>
-      <c r="AA25" t="inlineStr"/>
-      <c r="AB25" t="inlineStr"/>
-      <c r="AC25" t="inlineStr"/>
-      <c r="AD25" t="inlineStr"/>
-      <c r="AE25" t="inlineStr"/>
-      <c r="AF25" t="inlineStr"/>
-      <c r="AG25" t="inlineStr"/>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>PROMISE NFR + bản gán nhãn lại</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>binary FR/NFR + NFR</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>BERT (NoRBERT)</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>75/25 phân tầng; 10-fold phân tầng; leave-one-project-out</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Một phần (có bỏ 1 câu trùng; nhắc PROMISE có câu trùng)</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>N (oversampling chỉ trên tập train)</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>weighted F1 + theo lớp</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>Y (paired t-test)</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>Y (Zenodo)</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>F1 tới 94%</t>
+        </is>
+      </c>
+      <c r="AC25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>2</v>
+      </c>
       <c r="AH25">
         <f>IF(COUNT(AC25:AG25)=5,SUM(AC25:AG25),"")</f>
         <v/>
       </c>
       <c r="AI25" t="inlineStr"/>
-      <c r="AJ25" t="inlineStr"/>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>Bài chuẩn nhất trong bộ · Claude đọc (độ chắc chắn: cao)</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3166,7 +4515,11 @@
           <t>Xử lý mất cân bằng</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr"/>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr"/>
@@ -3177,17 +4530,17 @@
       <c r="Z26" t="inlineStr"/>
       <c r="AA26" t="inlineStr"/>
       <c r="AB26" t="inlineStr"/>
-      <c r="AC26" t="inlineStr"/>
-      <c r="AD26" t="inlineStr"/>
-      <c r="AE26" t="inlineStr"/>
-      <c r="AF26" t="inlineStr"/>
-      <c r="AG26" t="inlineStr"/>
       <c r="AH26">
         <f>IF(COUNT(AC26:AG26)=5,SUM(AC26:AG26),"")</f>
         <v/>
       </c>
       <c r="AI26" t="inlineStr"/>
-      <c r="AJ26" t="inlineStr"/>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>Lạc đề: phân loại câu mơ hồ (clear vs ambiguous), không phải FR/NFR · Ví dụ làm đúng: SMOTE chỉ trên tập train · Claude đọc (độ chắc chắn: cao)</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3263,28 +4616,87 @@
           <t>Xử lý mất cân bằng</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr"/>
-      <c r="W27" t="inlineStr"/>
-      <c r="X27" t="inlineStr"/>
-      <c r="Y27" t="inlineStr"/>
-      <c r="Z27" t="inlineStr"/>
-      <c r="AA27" t="inlineStr"/>
-      <c r="AB27" t="inlineStr"/>
-      <c r="AC27" t="inlineStr"/>
-      <c r="AD27" t="inlineStr"/>
-      <c r="AE27" t="inlineStr"/>
-      <c r="AF27" t="inlineStr"/>
-      <c r="AG27" t="inlineStr"/>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>PURE</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>multi-class (NFR)</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>SVM + ROS / SMOTE / các cách cân bằng</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>k-fold (so nhiều số fold)</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Y (chia ngẫu nhiên, không khử trùng)</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>không rõ (nghi trước khi chia: accuracy tăng 22–27%)</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>F1 + accuracy</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>accuracy +26,7% nhờ cân bằng lớp</t>
+        </is>
+      </c>
+      <c r="AC27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0</v>
+      </c>
       <c r="AH27">
         <f>IF(COUNT(AC27:AG27)=5,SUM(AC27:AG27),"")</f>
         <v/>
       </c>
       <c r="AI27" t="inlineStr"/>
-      <c r="AJ27" t="inlineStr"/>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>Mức tăng lớn đáng ngờ · Claude đọc (độ chắc chắn: thấp)</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3368,28 +4780,87 @@
           <t>Xử lý mất cân bằng</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr"/>
-      <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr"/>
-      <c r="W28" t="inlineStr"/>
-      <c r="X28" t="inlineStr"/>
-      <c r="Y28" t="inlineStr"/>
-      <c r="Z28" t="inlineStr"/>
-      <c r="AA28" t="inlineStr"/>
-      <c r="AB28" t="inlineStr"/>
-      <c r="AC28" t="inlineStr"/>
-      <c r="AD28" t="inlineStr"/>
-      <c r="AE28" t="inlineStr"/>
-      <c r="AF28" t="inlineStr"/>
-      <c r="AG28" t="inlineStr"/>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>PROMISE NFR mở rộng (6.086, 5 domain)</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>binary FR/NFR</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Đa phương thức + contrastive + domain adaptation</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>leave-one-domain-out (+ chia thường)</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>N (có đánh giá theo domain)</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>không dùng (augmentation cho contrastive)</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>F1 + accuracy</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>accuracy 95,8%, F1 95,4%</t>
+        </is>
+      </c>
+      <c r="AC28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0</v>
+      </c>
       <c r="AH28">
         <f>IF(COUNT(AC28:AG28)=5,SUM(AC28:AG28),"")</f>
         <v/>
       </c>
       <c r="AI28" t="inlineStr"/>
-      <c r="AJ28" t="inlineStr"/>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>Venue chất lượng không rõ; chỉ ablation, không kiểm định · Claude đọc (độ chắc chắn: thấp)</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3469,28 +4940,87 @@
           <t>Xử lý mất cân bằng</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
-      <c r="W29" t="inlineStr"/>
-      <c r="X29" t="inlineStr"/>
-      <c r="Y29" t="inlineStr"/>
-      <c r="Z29" t="inlineStr"/>
-      <c r="AA29" t="inlineStr"/>
-      <c r="AB29" t="inlineStr"/>
-      <c r="AC29" t="inlineStr"/>
-      <c r="AD29" t="inlineStr"/>
-      <c r="AE29" t="inlineStr"/>
-      <c r="AF29" t="inlineStr"/>
-      <c r="AG29" t="inlineStr"/>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>PROMISE + SecReq</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>binary FR/NFR + NFR + Sec</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>LLM prompting (GPT-4, Gemini, Llama…) so với fine-tuned</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>8:1:1 phân tầng, một lần</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Y (chia ngẫu nhiên, không khử trùng)</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>không dùng</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>macro-F1</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>Y (Scott-Knott ESD)</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>không rõ</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>GPT-4 macro-F1 0,73 (Sec)</t>
+        </is>
+      </c>
+      <c r="AC29" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>1</v>
+      </c>
       <c r="AH29">
         <f>IF(COUNT(AC29:AG29)=5,SUM(AC29:AG29),"")</f>
         <v/>
       </c>
       <c r="AI29" t="inlineStr"/>
-      <c r="AJ29" t="inlineStr"/>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>Claude đọc (độ chắc chắn: cao)</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3570,28 +5100,87 @@
           <t>Xử lý mất cân bằng</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr"/>
-      <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr"/>
-      <c r="W30" t="inlineStr"/>
-      <c r="X30" t="inlineStr"/>
-      <c r="Y30" t="inlineStr"/>
-      <c r="Z30" t="inlineStr"/>
-      <c r="AA30" t="inlineStr"/>
-      <c r="AB30" t="inlineStr"/>
-      <c r="AC30" t="inlineStr"/>
-      <c r="AD30" t="inlineStr"/>
-      <c r="AE30" t="inlineStr"/>
-      <c r="AF30" t="inlineStr"/>
-      <c r="AG30" t="inlineStr"/>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>PROMISE_exp (969)</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>multi-class (12 lớp)</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>LR, SVM… + SMOTE-Tomek</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>k-fold phân tầng</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Y (chia ngẫu nhiên, không khử trùng)</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>N (SMOTE-Tomek trong từng fold)</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>weighted F1 (recall = accuracy) + MCC</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>LR accuracy 76,2% ± 2,6%</t>
+        </is>
+      </c>
+      <c r="AC30" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>1</v>
+      </c>
       <c r="AH30">
         <f>IF(COUNT(AC30:AG30)=5,SUM(AC30:AG30),"")</f>
         <v/>
       </c>
       <c r="AI30" t="inlineStr"/>
-      <c r="AJ30" t="inlineStr"/>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>Preprint arXiv (chưa bình duyệt) · Claude đọc (độ chắc chắn: trung bình)</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3675,28 +5264,87 @@
           <t>Xử lý mất cân bằng</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr"/>
-      <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr"/>
-      <c r="W31" t="inlineStr"/>
-      <c r="X31" t="inlineStr"/>
-      <c r="Y31" t="inlineStr"/>
-      <c r="Z31" t="inlineStr"/>
-      <c r="AA31" t="inlineStr"/>
-      <c r="AB31" t="inlineStr"/>
-      <c r="AC31" t="inlineStr"/>
-      <c r="AD31" t="inlineStr"/>
-      <c r="AE31" t="inlineStr"/>
-      <c r="AF31" t="inlineStr"/>
-      <c r="AG31" t="inlineStr"/>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>SecReq, DOSSPRE, PROMISE+</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>binary (security vs non-security)</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>10 LLM + ML cổ điển</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>cross-project</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>N (chia theo project)</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>không dùng</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>P/R/F1</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>Y (replication package)</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>mistral-nemo F1 0,62 (cross-project)</t>
+        </is>
+      </c>
+      <c r="AC31" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>2</v>
+      </c>
       <c r="AH31">
         <f>IF(COUNT(AC31:AG31)=5,SUM(AC31:AG31),"")</f>
         <v/>
       </c>
       <c r="AI31" t="inlineStr"/>
-      <c r="AJ31" t="inlineStr"/>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>Nói thẳng: chia ngẫu nhiên có thể thổi phồng kết quả · Claude đọc (độ chắc chắn: cao)</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -3839,9 +5487,21 @@
           <t>RQ3(a)</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr"/>
-      <c r="K2" s="2" t="inlineStr"/>
-      <c r="L2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>15/26 chia ngẫu nhiên không khử trùng (R0007 R0018 R0060 R0125 R0187 R0406 R0517 R0538 R0617 R0618 R0625 R0632 R0655 R0719 R1202); 0/26 nhóm câu trùng khi chia; 5/26 không nêu cách chia</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>ĐỀ XUẤT: GAP CHÍNH (gộp với G2)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Mạnh nhất: không bài nào kiểm soát câu trùng; Allamanis 2019 (R1526) cho thấy câu trùng thổi phồng metric tới 100% ở bài toán code</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -3889,9 +5549,21 @@
           <t>Mới (bổ sung RQ3)</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="2" t="inlineStr"/>
-      <c r="L3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>7/26 dùng oversampling: 3 làm trước khi chia (R0187 R0538 R0632), 3 làm đúng trong train (R0181 R0517 R0719), 1 không rõ (R0618)</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>ĐỀ XUẤT: GAP CHÍNH (gộp với G1)</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Hai bài báo accuracy cao nhất bộ (R0632 98,79%, R0538 99%) đều oversampling trước khi chia; chưa bài nào đo mức thổi phồng</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -3939,9 +5611,21 @@
           <t>RQ1</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr"/>
-      <c r="K4" s="2" t="inlineStr"/>
-      <c r="L4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>6 bài ensemble: 4/6 không kiểm định (R0118 R0517 R0632 R1202); 2 bài có kiểm định (R0187 R0617) vẫn chia ngẫu nhiên không khử trùng</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>ĐỀ XUẤT: GAP PHỤ 1</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Câu hỏi: lợi thế ensemble có còn khi đánh giá có kiểm soát rò rỉ + kiểm định?</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -3989,8 +5673,16 @@
           <t>Hỗ trợ RQ1/RQ3</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr"/>
-      <c r="K5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>Macro-F1: 1/26 (R0655); weighted: 4/26; chỉ accuracy: 5/26</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>ĐỀ XUẤT: không thành RQ, làm đóng góp phương pháp (báo cáo macro-F1 + theo lớp)</t>
+        </is>
+      </c>
       <c r="L5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
@@ -4039,9 +5731,21 @@
           <t>RQ3(b)</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr"/>
-      <c r="K6" s="2" t="inlineStr"/>
-      <c r="L6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>4/26 đánh giá theo project / domain (R0164 R0637 R1341, R0181 leave-one-project-out)</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>ĐỀ XUẤT: GAP PHỤ 2 (nếu audit thấy PROMISE_exp đủ project)</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>R1341 nói thẳng chia ngẫu nhiên có thể thổi phồng kết quả</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -4089,8 +5793,16 @@
           <t>Hỗ trợ</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr"/>
-      <c r="K7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>5/26 công bố code/data (R0164 R0181 R0347 R0625 R1341)</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>ĐỀ XUẤT: không thành RQ, làm đóng góp (repo + dataset freeze)</t>
+        </is>
+      </c>
       <c r="L7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
@@ -4139,9 +5851,21 @@
           <t>RQ2</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr"/>
-      <c r="K8" s="2" t="inlineStr"/>
-      <c r="L8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1/26 tách riêng ảnh hưởng tiền xử lý (R0125, Abad et al. 2017)</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>ĐỀ XUẤT: BỎ khỏi RQ chính (đã có Abad 2017); giữ P0 làm cấu hình mặc định</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>Bỏ RQ2 tiền xử lý của v1.1 giúp giảm 2/3 số cấu hình</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
